--- a/CAD/electrical/main_board_v2/bom.xlsx
+++ b/CAD/electrical/main_board_v2/bom.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="main_board" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="main_board" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -394,7 +394,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -411,10 +411,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,13 +423,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.29"/>
@@ -539,7 +641,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
@@ -633,7 +735,7 @@
       <c r="C14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>53</v>
       </c>
     </row>
@@ -689,7 +791,7 @@
       <c r="C18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>66</v>
       </c>
     </row>
@@ -824,8 +926,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>